--- a/server/excel/release/lunar-newyear-event.xlsx
+++ b/server/excel/release/lunar-newyear-event.xlsx
@@ -881,7 +881,7 @@
     <t xml:space="preserve">chunjie_men</t>
   </si>
   <si>
-    <t xml:space="preserve">Trong cửa hàng sẽ ngẫu nhiên xoát ra thương phẩm, nhưng tiêu hao Nguyên bảo mua</t>
+    <t xml:space="preserve">Trong cửa hàng sẽ ngẫu nhiên xoát ra thương phẩm, nhưng tiêu hao Kim cương mua</t>
   </si>
   <si>
     <t xml:space="preserve">4:606008:50#4:606009:50#4:606010:50#4:606002:50#3:100025:1#3:400040:1#3:100098:100#3:100029:10#3:100214:1</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">Chúc phúc</t>
   </si>
   <si>
-    <t xml:space="preserve">Gia tăng 100-600 Nguyên bảo</t>
+    <t xml:space="preserve">Gia tăng 100-600 Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">chunjie_hongbao</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được 100-600 Nguyên bảo</t>
+    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được 100-600 Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:100#0:1:200#0:1:300#0:1:400#0:1:500#0:1:600</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguyên bảo nhiều hơn</t>
+    <t xml:space="preserve">Kim cương nhiều hơn</t>
   </si>
   <si>
     <t xml:space="preserve">Ngục giam</t>
